--- a/MinMax/scripts/comparison/accuracy_comparison_table_57_2_inference.xlsx
+++ b/MinMax/scripts/comparison/accuracy_comparison_table_57_2_inference.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Pg Vm Model False</t>
   </si>
@@ -31,82 +31,85 @@
     <t>Metric [MSE]</t>
   </si>
   <si>
+    <t>vi_tot</t>
+  </si>
+  <si>
+    <t>Ibr_from_r_tot</t>
+  </si>
+  <si>
+    <t>vr_tot</t>
+  </si>
+  <si>
+    <t>qinj_tot</t>
+  </si>
+  <si>
+    <t>qg_tot</t>
+  </si>
+  <si>
     <t>pd_tot</t>
   </si>
   <si>
+    <t>Ibr_from_i_tot</t>
+  </si>
+  <si>
+    <t>Ibr_to_i_tot</t>
+  </si>
+  <si>
+    <t>sample_num</t>
+  </si>
+  <si>
+    <t>qd_tot</t>
+  </si>
+  <si>
+    <t>pinj_tot</t>
+  </si>
+  <si>
+    <t>Iinj_r_tot</t>
+  </si>
+  <si>
+    <t>slack_tot</t>
+  </si>
+  <si>
     <t>nn_input</t>
   </si>
   <si>
+    <t>cost_tot</t>
+  </si>
+  <si>
+    <t>Ibr_to_r_tot</t>
+  </si>
+  <si>
     <t>pg_tot</t>
   </si>
   <si>
     <t>Iinj_i_tot</t>
   </si>
   <si>
-    <t>Iinj_r_tot</t>
-  </si>
-  <si>
-    <t>cost_tot</t>
-  </si>
-  <si>
-    <t>vi_tot</t>
-  </si>
-  <si>
-    <t>qg_tot</t>
-  </si>
-  <si>
-    <t>Ibr_from_i_tot</t>
-  </si>
-  <si>
-    <t>slack_tot</t>
-  </si>
-  <si>
-    <t>qd_tot</t>
-  </si>
-  <si>
-    <t>pinj_tot</t>
-  </si>
-  <si>
-    <t>Ibr_from_r_tot</t>
-  </si>
-  <si>
-    <t>vr_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_i_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_r_tot</t>
-  </si>
-  <si>
-    <t>qinj_tot</t>
-  </si>
-  <si>
     <t>vm_tot</t>
   </si>
   <si>
-    <t>23299.90 (23677.68 &gt; 1.61%)</t>
-  </si>
-  <si>
-    <t>1.95 (2.45)</t>
-  </si>
-  <si>
-    <t>23394.71 (23677.68 &gt; 1.20%)</t>
-  </si>
-  <si>
-    <t>1.89 (2.45)</t>
-  </si>
-  <si>
-    <t>22623.22 (23677.68 &gt; 4.44%)</t>
-  </si>
-  <si>
-    <t>-0.32 (2.45)</t>
-  </si>
-  <si>
-    <t>23475.59 (23677.68 &gt; 1.35%)</t>
+    <t>1.96 (2.45)</t>
+  </si>
+  <si>
+    <t>24018.73 (24474.61 &gt; 1.86%)</t>
+  </si>
+  <si>
+    <t>1.90 (2.45)</t>
+  </si>
+  <si>
+    <t>24109.94 (24474.61 &gt; 1.49%)</t>
+  </si>
+  <si>
+    <t>-0.33 (2.45)</t>
+  </si>
+  <si>
+    <t>23238.36 (24474.61 &gt; 5.05%)</t>
   </si>
   <si>
     <t>-0.31 (2.45)</t>
+  </si>
+  <si>
+    <t>23950.50 (24474.61 &gt; 2.14%)</t>
   </si>
 </sst>
 </file>
@@ -464,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -489,16 +492,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.01234189700335264</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>0.01233800873160362</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>6.995889270910993E-05</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>0.0001353621046291664</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -506,16 +509,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>0.04861924452242294</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>0.04860586420606024</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>0.01958103477954865</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>0.01138992700725794</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -523,16 +526,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>0.002241549256028894</v>
+        <v>0.001550194574519992</v>
       </c>
       <c r="C4">
-        <v>0.004825283842230825</v>
+        <v>0.001549973501823843</v>
       </c>
       <c r="D4">
-        <v>0.172685518860817</v>
+        <v>4.687027103500441E-05</v>
       </c>
       <c r="E4">
-        <v>0.2913502156734467</v>
+        <v>0.0001446967216907069</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -540,16 +543,16 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>0.02947992029148483</v>
+        <v>0.06158772483468056</v>
       </c>
       <c r="C5">
-        <v>0.02948137878751431</v>
+        <v>0.06158490478992462</v>
       </c>
       <c r="D5">
-        <v>0.006030238699167967</v>
+        <v>0.005088494159281254</v>
       </c>
       <c r="E5">
-        <v>0.01321580074727535</v>
+        <v>0.01442794408649206</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -557,33 +560,33 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>0.08768951571017602</v>
+        <v>0.3425398766994476</v>
       </c>
       <c r="C6">
-        <v>0.08765593138580018</v>
+        <v>0.3425398766994476</v>
       </c>
       <c r="D6">
-        <v>0.09222745895385742</v>
+        <v>0.03445430099964142</v>
       </c>
       <c r="E6">
-        <v>0.03599392995238304</v>
+        <v>0.06073655933141708</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" t="s">
-        <v>29</v>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -591,16 +594,16 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>0.01217474229633808</v>
+        <v>0.007715361283189428</v>
       </c>
       <c r="C8">
-        <v>0.01217108871787786</v>
+        <v>0.007715610395080455</v>
       </c>
       <c r="D8">
-        <v>7.201886182883754E-05</v>
+        <v>0.001831037574447691</v>
       </c>
       <c r="E8">
-        <v>0.0001300482690567151</v>
+        <v>0.003397703869268298</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -608,50 +611,38 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>0.3031262457370758</v>
+        <v>0.0076170077628763</v>
       </c>
       <c r="C9">
-        <v>0.3031262457370758</v>
+        <v>0.00761727108427651</v>
       </c>
       <c r="D9">
-        <v>0.03599422425031662</v>
+        <v>0.001779218204319477</v>
       </c>
       <c r="E9">
-        <v>0.0538790225982666</v>
+        <v>0.003376286011189222</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B10">
-        <v>0.008139271923712735</v>
-      </c>
-      <c r="C10">
-        <v>0.008139463594457805</v>
-      </c>
-      <c r="D10">
-        <v>0.001930019585415721</v>
-      </c>
-      <c r="E10">
-        <v>0.003086020704358816</v>
-      </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" t="s">
-        <v>30</v>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -659,16 +650,16 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>0.1060227379202843</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>0.1059909388422966</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>0.09181498736143112</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>0.04282952100038528</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -676,33 +667,33 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>0.09441745281219482</v>
+        <v>0.0986421036498919</v>
       </c>
       <c r="C13">
-        <v>0.09438345581293106</v>
+        <v>0.09861060414589765</v>
       </c>
       <c r="D13">
-        <v>0.09277228266000748</v>
+        <v>0.09133849292993546</v>
       </c>
       <c r="E13">
-        <v>0.03678359836339951</v>
+        <v>0.04224969819188118</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B14">
-        <v>0.04357688729311793</v>
-      </c>
-      <c r="C14">
-        <v>0.04356236526276611</v>
-      </c>
-      <c r="D14">
-        <v>0.02003084868192673</v>
-      </c>
-      <c r="E14">
-        <v>0.009772884659469128</v>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -710,33 +701,33 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>0.001653312821872532</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>0.001653099898248911</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>4.961290687788278E-05</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>0.000162059921422042</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B16">
-        <v>0.008033861828951055</v>
-      </c>
-      <c r="C16">
-        <v>0.008034066721636725</v>
-      </c>
-      <c r="D16">
-        <v>0.001874515786767006</v>
-      </c>
-      <c r="E16">
-        <v>0.003058716421946883</v>
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -744,16 +735,16 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>0.04344614906408591</v>
+        <v>0.04851562779027467</v>
       </c>
       <c r="C17">
-        <v>0.04343164728555226</v>
+        <v>0.04850226449253603</v>
       </c>
       <c r="D17">
-        <v>0.02015913277864456</v>
+        <v>0.01970735564827919</v>
       </c>
       <c r="E17">
-        <v>0.009745525196194649</v>
+        <v>0.01136565208435059</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -761,16 +752,16 @@
         <v>21</v>
       </c>
       <c r="B18">
-        <v>0.06075229868292809</v>
+        <v>0.002496927501852147</v>
       </c>
       <c r="C18">
-        <v>0.06074992567300797</v>
+        <v>0.004875362395457512</v>
       </c>
       <c r="D18">
-        <v>0.00507386913523078</v>
+        <v>0.1729633659124374</v>
       </c>
       <c r="E18">
-        <v>0.01206081919372082</v>
+        <v>0.35335773229599</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -778,16 +769,33 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>0.0008237383444793522</v>
+        <v>0.02785107521212342</v>
       </c>
       <c r="C19">
-        <v>0.0008237410802394152</v>
+        <v>0.02785272707882295</v>
       </c>
       <c r="D19">
-        <v>4.777800859301351E-05</v>
+        <v>0.005843071732670069</v>
       </c>
       <c r="E19">
-        <v>0.000151216343510896</v>
+        <v>0.01470148842781782</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20">
+        <v>0.0007680971175432205</v>
+      </c>
+      <c r="C20">
+        <v>0.000768100842833519</v>
+      </c>
+      <c r="D20">
+        <v>4.512624582275748E-05</v>
+      </c>
+      <c r="E20">
+        <v>0.0001352050894638523</v>
       </c>
     </row>
   </sheetData>
